--- a/四均線起漲圖表_20260616/四均線起漲精選_20260616.xlsx
+++ b/四均線起漲圖表_20260616/四均線起漲精選_20260616.xlsx
@@ -542,30 +542,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6179.TWO</t>
+          <t>6191.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>亞通</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>25.3</v>
+        <v>103</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4043</v>
+        <v>21025</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1797</v>
+        <v>8048</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
